--- a/config/excel/upgrade_fx.xlsx
+++ b/config/excel/upgrade_fx.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="upgrade_fx" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -508,7 +508,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
